--- a/04-templates/files/01-credentialing-tracker.xlsx
+++ b/04-templates/files/01-credentialing-tracker.xlsx
@@ -775,7 +775,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>The Marketing Pros  ·  themarketingpros.com  ·  Last updated: auto</t>
+          <t>Riverside Medical Group  ·  Sample Data — Replace with your practice name  ·  Last updated: auto</t>
         </is>
       </c>
     </row>
